--- a/example.xlsx
+++ b/example.xlsx
@@ -1,148 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chao/Documents/claude-code-test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F507A5B5-E89C-1D4A-A673-130321DEABE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19200" xr2:uid="{83BC02D5-EA12-4EB3-B214-E52C1D95CBC6}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19200" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
-  <si>
-    <t>Final Notice: 2026 AMC Payment due by April 15th</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colombo </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Dear "&amp;B2&amp;"
-Please find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.
-According to our records, payment for Invoice #«Invoice_Number» remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.
-Please review the attached letter for full details, including critical information regarding:
-mCloud Connectivity and Data Access
-New Currency Template releases
-Firmware &amp; Software security updates
-Remote Technical Support continuity
-Maintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.
-If you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;B3&amp;", or Lawrance Huang (lawrance.huang@automodules.com).
-Best regards,
-The Accounts Team
-Masterwork Automodules
-</t>
-  </si>
-  <si>
-    <t>2026_AMC_Notice1352.pdf</t>
-  </si>
-  <si>
-    <t>Ms. Mary Nassar</t>
-  </si>
-  <si>
-    <t>2026_AMC_Notice1351.pdf</t>
-  </si>
-  <si>
-    <t>Mr. Karim Wafik</t>
-  </si>
-  <si>
-    <t>Email Subject</t>
-  </si>
-  <si>
-    <t>Attachment</t>
-  </si>
-  <si>
-    <t>Email CC</t>
-  </si>
-  <si>
-    <t>E-mail</t>
-  </si>
-  <si>
-    <t>Attn</t>
-  </si>
-  <si>
-    <t>Sales</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">"Dear "&amp;B2&amp;"
-Please find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.
-According to our records, payment for Invoice #«Invoice_Number» remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.
-Please review the attached letter for full details, including critical information regarding:
-mCloud Connectivity and Data Access
-New Currency Template releases
-Firmware &amp; Software security updates
-Remote Technical Support continuity
-Maintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.
-If you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A2&amp;", or Lawrance Huang (lawrance.huang@automodules.com).
-Best regards,
-The Accounts Team
-Masterwork Automodules
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ysuper0412@gmail.com</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ysuper0412@yahoo.com.tw</t>
-  </si>
-  <si>
-    <t>Email Content</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ysuper.liang@automodules.tw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="新細明體"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -159,26 +59,85 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -444,90 +403,1881 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BDB7EE-7B11-4BF6-8771-5983C1AC6074}">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="43.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.19921875" customWidth="1"/>
-    <col min="5" max="5" width="64.19921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="48.796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="255.796875" bestFit="1" customWidth="1"/>
+    <col width="43.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="76.19921875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="42.19921875" customWidth="1" min="4" max="4"/>
+    <col width="64.19921875" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="48.796875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="255.796875" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>2</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Attn</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Email CC</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Email Subject</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Email Content</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mr. James Chen</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>james.chen@gmail.com</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>accounts@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1351.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B2&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1351 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A2&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ms. Sarah Kim</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sarah.kim@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>sales@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1352.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B3&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1352 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A3&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mr. Ali Hassan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ali.hassan@outlook.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>support@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1353.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B4&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1353 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A4&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ms. Maria Santos</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>maria.santos@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>billing@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1354.pdf</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B5&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1354 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A5&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mr. David Lim</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>david.lim@company.net</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>lawrance.huang@automodules.com</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1355.pdf</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B6&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1355 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A6&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ms. Priya Patel</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>priya.patel@business.org</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1356.pdf</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B7&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1356 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A7&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mr. Omar Abdullah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>omar.abdullah@gmail.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>accounts@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1357.pdf</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B8&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1357 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A8&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ms. Linda Tan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>linda.tan@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>sales@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1358.pdf</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B9&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1358 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A9&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mr. Kevin Wong</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>kevin.wong@outlook.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>support@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1359.pdf</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B10&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1359 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A10&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ms. Fatima Al-Rashid</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fatima.alrashid@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>billing@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1360.pdf</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B11&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1360 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A11&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mr. Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>carlos.rivera@company.net</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>lawrance.huang@automodules.com</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1361.pdf</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B12&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1361 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A12&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ms. Aisha Mohammed</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>aisha.mohammed@business.org</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1362.pdf</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B13&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1362 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A13&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mr. Peter Nakamura</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>peter.nakamura@gmail.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>accounts@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1363.pdf</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B14&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1363 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A14&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ms. Grace Okonkwo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>grace.okonkwo@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sales@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1364.pdf</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B15&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1364 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A15&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mr. Ahmed Khalil</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ahmed.khalil@outlook.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>support@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1365.pdf</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B16&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1365 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A16&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ms. Yu Mei</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>yu.mei@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>billing@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1366.pdf</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B17&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1366 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A17&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mr. Samuel Adeyemi</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>samuel.adeyemi@company.net</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>lawrance.huang@automodules.com</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1367.pdf</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B18&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1367 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A18&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ms. Elena Popescu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>elena.popescu@business.org</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1368.pdf</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B19&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1368 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A19&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Mr. Ravi Sharma</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ravi.sharma@gmail.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>accounts@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1369.pdf</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B20&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1369 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A20&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ms. Nadia Ivanova</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>nadia.ivanova@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>sales@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1370.pdf</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B21&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1370 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A21&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Mr. John Mensah</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>john.mensah@outlook.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>support@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1371.pdf</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B22&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1371 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A22&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ms. Hana Suzuki</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>hana.suzuki@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>billing@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1372.pdf</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B23&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1372 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A23&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mr. Ibrahim Diallo</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ibrahim.diallo@company.net</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>lawrance.huang@automodules.com</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1373.pdf</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B24&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1373 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A24&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ms. Rosa Gutierrez</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>rosa.gutierrez@business.org</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1374.pdf</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B25&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1374 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A25&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mr. Chidi Obi</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>chidi.obi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>accounts@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1375.pdf</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B26&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1375 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A26&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ms. Layla Hassan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>layla.hassan@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sales@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1376.pdf</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B27&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1376 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A27&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mr. Yusuf Adama</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>yusuf.adama@outlook.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>support@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1377.pdf</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B28&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1377 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A28&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ms. Jin Li</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jin.li@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>billing@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1378.pdf</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B29&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1378 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A29&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mr. Kwame Asante</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>kwame.asante@company.net</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>lawrance.huang@automodules.com</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1379.pdf</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B30&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1379 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A30&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ms. Amara Diop</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>amara.diop@business.org</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1380.pdf</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B31&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1380 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A31&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mr. Tariq Rahman</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>tariq.rahman@gmail.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>accounts@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1381.pdf</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B32&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1381 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A32&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ms. Sofia Alves</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>sofia.alves@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>sales@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1382.pdf</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B33&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1382 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A33&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Mr. Emmanuel Nwosu</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>emmanuel.nwosu@outlook.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>support@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1383.pdf</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B34&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1383 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A34&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ms. Mei-Ling Ho</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>meiling.ho@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>billing@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1384.pdf</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B35&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1384 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A35&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Mr. Bashir Saleh</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>bashir.saleh@company.net</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>lawrance.huang@automodules.com</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1385.pdf</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B36&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1385 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A36&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ms. Valentina Cruz</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>valentina.cruz@business.org</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1386.pdf</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B37&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1386 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A37&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mr. Sipho Dlamini</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sipho.dlamini@gmail.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>accounts@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1387.pdf</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B38&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1387 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A38&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ms. Nour El-Din</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>nour.eldin@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>sales@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1388.pdf</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B39&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1388 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A39&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Mr. Tran Van Minh</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>tran.van.minh@outlook.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>support@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1389.pdf</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B40&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1389 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A40&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ms. Zara Ahmed</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>zara.ahmed@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>billing@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1390.pdf</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B41&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1390 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A41&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mr. Felix Boateng</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>felix.boateng@company.net</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>lawrance.huang@automodules.com</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1391.pdf</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B42&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1391 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A42&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Jakarta</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ms. Ana Pereira</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ana.pereira@business.org</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1392.pdf</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B43&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1392 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A43&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Manila</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mr. Mustafa Ozkan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>mustafa.ozkan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>accounts@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1393.pdf</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B44&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1393 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A44&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ms. Yuki Tanaka</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>yuki.tanaka@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>sales@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1394.pdf</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B45&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1394 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A45&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mr. Kofi Mensah</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>kofi.mensah@outlook.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>support@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1395.pdf</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B46&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1395 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A46&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ms. Ingrid Berg</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ingrid.berg@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>billing@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1396.pdf</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B47&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1396 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A47&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mr. Faisal Al-Amri</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>faisal.alamri@company.net</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>lawrance.huang@automodules.com</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1397.pdf</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B48&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1397 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A48&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Dhaka</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ms. Carmen Lopez</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>carmen.lopez@business.org</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1398.pdf</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B49&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1398 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A49&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Mr. Theo Papadopoulos</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>theo.papadopoulos@gmail.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>accounts@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1399.pdf</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B50&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1399 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A50&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ms. Ling Zhang</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ling.zhang@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>sales@automodules.tw</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026_AMC_Notice1400.pdf</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Final Notice: 2026 AMC Payment due by April 15th</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>"Dear "&amp;B51&amp;"\n\nPlease find the attached formal notification regarding the outstanding 2026 Annual Maintenance Charge (AMC) for your account.\n\nAccording to our records, payment for Invoice #1400 remains unsettled. To avoid any disruption to your business operations, we kindly request that this balance be cleared by April 15th, 2026.\n\nPlease review the attached letter for full details, including critical information regarding:\n\nmCloud Connectivity and Data Access\n\nNew Currency Template releases\n\nFirmware &amp; Software security updates\n\nRemote Technical Support continuity\n\nMaintaining an active AMC is essential to mitigate operational risks and ensure your machines remain market-ready.\n\nIf you have already processed this payment, please reply with a copy of the remittance advice so we can update your status. For any questions, please contact your dedicated Sales Representative "&amp;A51&amp;", or Lawrance Huang (lawrance.huang@automodules.com).\n\nBest regards,\n\nThe Accounts Team\nMasterwork Automodules\n"</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{FADE2790-D34E-A249-B8C5-6B0F9AF6388E}"/>
-    <hyperlink ref="D2" r:id="rId2" xr:uid="{9044CB76-7955-9C4D-89FC-142048959133}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
